--- a/isms-core-framework/A.8-technological-controls/isms-a.8.17-clock-synchronization/WKBK/90_workbooks/ISMS-IMP-A.8.17.4_Time_Sync_Dashboard_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.17-clock-synchronization/WKBK/90_workbooks/ISMS-IMP-A.8.17.4_Time_Sync_Dashboard_20260208.xlsx
@@ -566,7 +566,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-02-08 11:49:49</t>
+          <t>Generated: 2026-02-08 12:26:17</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-02-08 11:49:49</t>
+          <t>Generated: 2026-02-08 12:26:17</t>
         </is>
       </c>
     </row>
